--- a/datasets/treinamento.xlsx
+++ b/datasets/treinamento.xlsx
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
@@ -2352,16 +2352,16 @@
         <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2695,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>1</v>
@@ -3088,10 +3088,10 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -5051,16 +5051,16 @@
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -7567,7 +7567,7 @@
         <v>1</v>
       </c>
       <c r="L105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -7576,7 +7576,7 @@
         <v>1</v>
       </c>
       <c r="O105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
@@ -7594,7 +7594,7 @@
         <v>1</v>
       </c>
       <c r="U105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V105" t="n">
         <v>0</v>
